--- a/物联网/指标/2025/8月/【分管副总考核&KPI】县市收入202508(3).xlsx
+++ b/物联网/指标/2025/8月/【分管副总考核&KPI】县市收入202508(3).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\嘉兴移动\政企\物联网\指标\2025\8月\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CCFD8E-5EAB-4596-AAB2-B7B032015184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E5809B-08F8-42DB-B199-600A8049E9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1605" yWindow="870" windowWidth="21765" windowHeight="13950" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="1440" windowWidth="21765" windowHeight="13950" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="汇总" sheetId="3" r:id="rId1"/>
@@ -41,11 +41,12 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{3616507C-DB22-44A4-8D6F-E9ABE266B9D5}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -54,11 +55,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{472835D6-7BEE-4488-852D-D70A33479598}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -67,11 +69,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{3E1F57A9-4D35-459C-83DD-2435E4BE5455}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -80,11 +83,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{DE2DCB6B-0200-45DC-9D85-447879FABFA9}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
+            <color indexed="81"/>
             <rFont val="宋体"/>
             <family val="3"/>
             <charset val="134"/>
@@ -744,7 +748,7 @@
     <numFmt numFmtId="183" formatCode="0_ "/>
     <numFmt numFmtId="184" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -862,6 +866,13 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="17">
@@ -1306,15 +1317,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1334,6 +1336,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2198,7 +2209,7 @@
       </c>
       <c r="B21" s="66">
         <f>物联网!B4+物联网!C4+物联网!D4</f>
-        <v>827.60000000000025</v>
+        <v>830.30000000000007</v>
       </c>
       <c r="C21" s="66">
         <f>物联网!E4+物联网!F4+物联网!G4+物联网!H4+物联网!I4+物联网!J4</f>
@@ -2212,7 +2223,7 @@
       </c>
       <c r="F21" s="66">
         <f t="shared" ref="F21:F28" si="4">SUM(B21:E21)</f>
-        <v>1020.2254896603772</v>
+        <v>1022.925489660377</v>
       </c>
       <c r="G21" s="33">
         <f>物联网!N4</f>
@@ -2233,7 +2244,7 @@
       </c>
       <c r="B22" s="66">
         <f>物联网!B5+物联网!C5+物联网!D5</f>
-        <v>352.9</v>
+        <v>386.2</v>
       </c>
       <c r="C22" s="66">
         <f>物联网!E5+物联网!F5+物联网!G5+物联网!H5+物联网!I5+物联网!J5</f>
@@ -2247,7 +2258,7 @@
       </c>
       <c r="F22" s="66">
         <f t="shared" si="4"/>
-        <v>406.597488</v>
+        <v>439.89748800000001</v>
       </c>
       <c r="G22" s="33">
         <f>物联网!N5</f>
@@ -2268,7 +2279,7 @@
       </c>
       <c r="B23" s="66">
         <f>物联网!B6+物联网!C6+物联网!D6</f>
-        <v>266.8</v>
+        <v>295.50000000000006</v>
       </c>
       <c r="C23" s="66">
         <f>物联网!E6+物联网!F6+物联网!G6+物联网!H6+物联网!I6+物联网!J6</f>
@@ -2282,7 +2293,7 @@
       </c>
       <c r="F23" s="66">
         <f t="shared" si="4"/>
-        <v>503.52579979245303</v>
+        <v>532.22579979245302</v>
       </c>
       <c r="G23" s="33">
         <f>物联网!N6</f>
@@ -2303,7 +2314,7 @@
       </c>
       <c r="B24" s="66">
         <f>物联网!B7+物联网!C7+物联网!D7</f>
-        <v>254.5</v>
+        <v>252.29999999999998</v>
       </c>
       <c r="C24" s="66">
         <f>物联网!E7+物联网!F7+物联网!G7+物联网!H7+物联网!I7+物联网!J7</f>
@@ -2317,7 +2328,7 @@
       </c>
       <c r="F24" s="66">
         <f t="shared" si="4"/>
-        <v>3291.504055332075</v>
+        <v>3289.3040553320748</v>
       </c>
       <c r="G24" s="33">
         <f>物联网!N7</f>
@@ -2338,7 +2349,7 @@
       </c>
       <c r="B25" s="66">
         <f>物联网!B8+物联网!C8+物联网!D8</f>
-        <v>1007.96</v>
+        <v>1007.95</v>
       </c>
       <c r="C25" s="66">
         <f>物联网!E8+物联网!F8+物联网!G8+物联网!H8+物联网!I8+物联网!J8</f>
@@ -2352,7 +2363,7 @@
       </c>
       <c r="F25" s="66">
         <f t="shared" si="4"/>
-        <v>1383.1103512830189</v>
+        <v>1383.1003512830189</v>
       </c>
       <c r="G25" s="33">
         <f>物联网!N8</f>
@@ -2408,7 +2419,7 @@
       </c>
       <c r="B27" s="66">
         <f>物联网!B10+物联网!C10+物联网!D10</f>
-        <v>270.2</v>
+        <v>307.5</v>
       </c>
       <c r="C27" s="66">
         <f>物联网!E10+物联网!F10+物联网!G10+物联网!H10+物联网!I10+物联网!J10</f>
@@ -2422,7 +2433,7 @@
       </c>
       <c r="F27" s="66">
         <f t="shared" si="4"/>
-        <v>429.155946735849</v>
+        <v>466.45594673584901</v>
       </c>
       <c r="G27" s="33">
         <f>物联网!N10</f>
@@ -2443,7 +2454,7 @@
       </c>
       <c r="B28" s="66">
         <f>物联网!B11+物联网!C11+物联网!D11</f>
-        <v>4181.21</v>
+        <v>4324.7</v>
       </c>
       <c r="C28" s="66">
         <f>物联网!E11+物联网!F11+物联网!G11+物联网!H11+物联网!I11+物联网!J11</f>
@@ -2457,7 +2468,7 @@
       </c>
       <c r="F28" s="66">
         <f t="shared" si="4"/>
-        <v>8666.0915000000005</v>
+        <v>8809.5815000000002</v>
       </c>
       <c r="G28" s="33">
         <f>SUM(G21:G27)</f>
@@ -2743,7 +2754,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="23">
-        <v>740.4000000000002</v>
+        <v>743.1</v>
       </c>
       <c r="C4" s="24">
         <v>21.7</v>
@@ -2771,11 +2782,11 @@
       </c>
       <c r="K4" s="49">
         <f t="shared" ref="K4:K11" si="0">SUM(B4:D4)</f>
-        <v>827.60000000000025</v>
+        <v>830.30000000000007</v>
       </c>
       <c r="L4" s="50">
         <f t="shared" ref="L4:L11" si="1">SUM(B4:J4)</f>
-        <v>1007.7294056603776</v>
+        <v>1010.4294056603774</v>
       </c>
       <c r="M4" s="37"/>
       <c r="N4" s="32">
@@ -2796,7 +2807,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="23">
-        <v>269.2</v>
+        <v>302.5</v>
       </c>
       <c r="C5" s="24">
         <v>28.4</v>
@@ -2824,11 +2835,11 @@
       </c>
       <c r="K5" s="49">
         <f t="shared" si="0"/>
-        <v>352.9</v>
+        <v>386.2</v>
       </c>
       <c r="L5" s="50">
         <f t="shared" si="1"/>
-        <v>394.4609999999999</v>
+        <v>427.76099999999991</v>
       </c>
       <c r="M5" s="37"/>
       <c r="N5" s="32">
@@ -2849,7 +2860,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="23">
-        <v>204.1</v>
+        <v>232.8</v>
       </c>
       <c r="C6" s="24">
         <v>33.6</v>
@@ -2877,11 +2888,11 @@
       </c>
       <c r="K6" s="49">
         <f t="shared" si="0"/>
-        <v>266.8</v>
+        <v>295.50000000000006</v>
       </c>
       <c r="L6" s="50">
         <f t="shared" si="1"/>
-        <v>471.46888679245279</v>
+        <v>500.16888679245284</v>
       </c>
       <c r="M6" s="37"/>
       <c r="N6" s="32">
@@ -2902,7 +2913,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="23">
-        <v>212.8</v>
+        <v>210.6</v>
       </c>
       <c r="C7" s="24">
         <v>31</v>
@@ -2930,11 +2941,11 @@
       </c>
       <c r="K7" s="49">
         <f t="shared" si="0"/>
-        <v>254.5</v>
+        <v>252.29999999999998</v>
       </c>
       <c r="L7" s="50">
         <f t="shared" si="1"/>
-        <v>372.22398113207544</v>
+        <v>370.02398113207551</v>
       </c>
       <c r="M7" s="37"/>
       <c r="N7" s="32">
@@ -2955,7 +2966,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="23">
-        <v>863.86</v>
+        <v>863.85</v>
       </c>
       <c r="C8" s="24">
         <v>116.4</v>
@@ -2983,11 +2994,11 @@
       </c>
       <c r="K8" s="49">
         <f t="shared" si="0"/>
-        <v>1007.96</v>
+        <v>1007.95</v>
       </c>
       <c r="L8" s="50">
         <f t="shared" si="1"/>
-        <v>1378.1942452830192</v>
+        <v>1378.1842452830192</v>
       </c>
       <c r="M8" s="37"/>
       <c r="N8" s="32">
@@ -3061,7 +3072,7 @@
         <v>49</v>
       </c>
       <c r="B10" s="23">
-        <v>256.7</v>
+        <v>294</v>
       </c>
       <c r="C10" s="24">
         <v>11.3</v>
@@ -3089,11 +3100,11 @@
       </c>
       <c r="K10" s="49">
         <f t="shared" si="0"/>
-        <v>270.2</v>
+        <v>307.5</v>
       </c>
       <c r="L10" s="50">
         <f t="shared" si="1"/>
-        <v>411.41603773584865</v>
+        <v>448.71603773584866</v>
       </c>
       <c r="M10" s="37"/>
       <c r="N10" s="32">
@@ -3114,7 +3125,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="26">
-        <v>3640.31</v>
+        <v>3783.8</v>
       </c>
       <c r="C11" s="24">
         <f t="shared" ref="C11:J11" si="2">SUM(C4:C10)</f>
@@ -3150,11 +3161,11 @@
       </c>
       <c r="K11" s="49">
         <f t="shared" si="0"/>
-        <v>4181.21</v>
+        <v>4324.7</v>
       </c>
       <c r="L11" s="50">
         <f t="shared" si="1"/>
-        <v>5637.7275000000054</v>
+        <v>5781.2175000000052</v>
       </c>
       <c r="M11" s="37"/>
       <c r="N11" s="33">
@@ -6036,7 +6047,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="3"/>
-      <c r="C1" s="91" t="s">
+      <c r="C1" s="88" t="s">
         <v>76</v>
       </c>
       <c r="D1" s="82" t="s">
@@ -6060,7 +6071,7 @@
     <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="82"/>
       <c r="B2" s="4"/>
-      <c r="C2" s="92"/>
+      <c r="C2" s="89"/>
       <c r="D2" s="2" t="s">
         <v>81</v>
       </c>
@@ -6390,7 +6401,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="91" t="s">
+      <c r="C15" s="88" t="s">
         <v>76</v>
       </c>
       <c r="D15" s="82" t="s">
@@ -6414,7 +6425,7 @@
     <row r="16" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A16" s="82"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="92"/>
+      <c r="C16" s="89"/>
       <c r="D16" s="2" t="s">
         <v>81</v>
       </c>
@@ -6744,7 +6755,7 @@
         <v>1</v>
       </c>
       <c r="B29" s="3"/>
-      <c r="C29" s="91" t="s">
+      <c r="C29" s="88" t="s">
         <v>85</v>
       </c>
       <c r="D29" s="82" t="s">
@@ -6768,7 +6779,7 @@
     <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A30" s="82"/>
       <c r="B30" s="4"/>
-      <c r="C30" s="92"/>
+      <c r="C30" s="89"/>
       <c r="D30" s="2" t="s">
         <v>81</v>
       </c>
@@ -7099,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="B41" s="3"/>
-      <c r="C41" s="91" t="s">
+      <c r="C41" s="88" t="s">
         <v>89</v>
       </c>
       <c r="D41" s="82" t="s">
@@ -7123,7 +7134,7 @@
     <row r="42" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A42" s="82"/>
       <c r="B42" s="4"/>
-      <c r="C42" s="92"/>
+      <c r="C42" s="89"/>
       <c r="D42" s="2" t="s">
         <v>81</v>
       </c>
@@ -7454,7 +7465,7 @@
         <v>1</v>
       </c>
       <c r="B53" s="3"/>
-      <c r="C53" s="91" t="s">
+      <c r="C53" s="88" t="s">
         <v>89</v>
       </c>
       <c r="D53" s="82" t="s">
@@ -7478,7 +7489,7 @@
     <row r="54" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A54" s="82"/>
       <c r="B54" s="4"/>
-      <c r="C54" s="92"/>
+      <c r="C54" s="89"/>
       <c r="D54" s="2" t="s">
         <v>81</v>
       </c>
@@ -7809,7 +7820,7 @@
         <v>1</v>
       </c>
       <c r="B65" s="3"/>
-      <c r="C65" s="91" t="s">
+      <c r="C65" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D65" s="82" t="s">
@@ -7833,7 +7844,7 @@
     <row r="66" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A66" s="82"/>
       <c r="B66" s="4"/>
-      <c r="C66" s="92"/>
+      <c r="C66" s="89"/>
       <c r="D66" s="2" t="s">
         <v>81</v>
       </c>
@@ -8164,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="B78" s="3"/>
-      <c r="C78" s="91" t="s">
+      <c r="C78" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D78" s="82" t="s">
@@ -8188,7 +8199,7 @@
     <row r="79" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A79" s="82"/>
       <c r="B79" s="4"/>
-      <c r="C79" s="92"/>
+      <c r="C79" s="89"/>
       <c r="D79" s="2" t="s">
         <v>81</v>
       </c>
@@ -8519,7 +8530,7 @@
         <v>1</v>
       </c>
       <c r="B91" s="3"/>
-      <c r="C91" s="91" t="s">
+      <c r="C91" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D91" s="82" t="s">
@@ -8543,7 +8554,7 @@
     <row r="92" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A92" s="82"/>
       <c r="B92" s="4"/>
-      <c r="C92" s="92"/>
+      <c r="C92" s="89"/>
       <c r="D92" s="2" t="s">
         <v>81</v>
       </c>
@@ -8874,7 +8885,7 @@
         <v>1</v>
       </c>
       <c r="B104" s="3"/>
-      <c r="C104" s="91" t="s">
+      <c r="C104" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D104" s="82" t="s">
@@ -8898,7 +8909,7 @@
     <row r="105" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A105" s="82"/>
       <c r="B105" s="4"/>
-      <c r="C105" s="92"/>
+      <c r="C105" s="89"/>
       <c r="D105" s="2" t="s">
         <v>81</v>
       </c>
@@ -9229,7 +9240,7 @@
         <v>1</v>
       </c>
       <c r="B117" s="3"/>
-      <c r="C117" s="91" t="s">
+      <c r="C117" s="88" t="s">
         <v>93</v>
       </c>
       <c r="D117" s="82" t="s">
@@ -9253,7 +9264,7 @@
     <row r="118" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A118" s="82"/>
       <c r="B118" s="4"/>
-      <c r="C118" s="92"/>
+      <c r="C118" s="89"/>
       <c r="D118" s="2" t="s">
         <v>81</v>
       </c>
@@ -9584,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="B130" s="3"/>
-      <c r="C130" s="91" t="s">
+      <c r="C130" s="88" t="s">
         <v>97</v>
       </c>
       <c r="D130" s="82" t="s">
@@ -9608,7 +9619,7 @@
     <row r="131" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A131" s="82"/>
       <c r="B131" s="4"/>
-      <c r="C131" s="92"/>
+      <c r="C131" s="89"/>
       <c r="D131" s="2" t="s">
         <v>81</v>
       </c>
@@ -9939,7 +9950,7 @@
         <v>1</v>
       </c>
       <c r="B143" s="3"/>
-      <c r="C143" s="91" t="s">
+      <c r="C143" s="88" t="s">
         <v>97</v>
       </c>
       <c r="D143" s="82" t="s">
@@ -9963,7 +9974,7 @@
     <row r="144" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A144" s="82"/>
       <c r="B144" s="4"/>
-      <c r="C144" s="92"/>
+      <c r="C144" s="89"/>
       <c r="D144" s="2" t="s">
         <v>81</v>
       </c>
@@ -10294,7 +10305,7 @@
         <v>1</v>
       </c>
       <c r="B156" s="3"/>
-      <c r="C156" s="91" t="s">
+      <c r="C156" s="88" t="s">
         <v>97</v>
       </c>
       <c r="D156" s="82" t="s">
@@ -10318,7 +10329,7 @@
     <row r="157" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A157" s="82"/>
       <c r="B157" s="4"/>
-      <c r="C157" s="92"/>
+      <c r="C157" s="89"/>
       <c r="D157" s="2" t="s">
         <v>81</v>
       </c>
@@ -10649,7 +10660,7 @@
         <v>1</v>
       </c>
       <c r="B169" s="3"/>
-      <c r="C169" s="91" t="s">
+      <c r="C169" s="88" t="s">
         <v>97</v>
       </c>
       <c r="D169" s="82" t="s">
@@ -10673,7 +10684,7 @@
     <row r="170" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A170" s="82"/>
       <c r="B170" s="4"/>
-      <c r="C170" s="92"/>
+      <c r="C170" s="89"/>
       <c r="D170" s="2" t="s">
         <v>81</v>
       </c>
@@ -11004,7 +11015,7 @@
         <v>1</v>
       </c>
       <c r="B181" s="3"/>
-      <c r="C181" s="91" t="s">
+      <c r="C181" s="88" t="s">
         <v>97</v>
       </c>
       <c r="D181" s="82" t="s">
@@ -11028,7 +11039,7 @@
     <row r="182" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A182" s="82"/>
       <c r="B182" s="4"/>
-      <c r="C182" s="92"/>
+      <c r="C182" s="89"/>
       <c r="D182" s="2" t="s">
         <v>81</v>
       </c>
@@ -11362,7 +11373,7 @@
         <v>1</v>
       </c>
       <c r="B194" s="3"/>
-      <c r="C194" s="91" t="s">
+      <c r="C194" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D194" s="82" t="s">
@@ -11386,7 +11397,7 @@
     <row r="195" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A195" s="82"/>
       <c r="B195" s="4"/>
-      <c r="C195" s="92"/>
+      <c r="C195" s="89"/>
       <c r="D195" s="2" t="s">
         <v>81</v>
       </c>
@@ -11717,7 +11728,7 @@
         <v>1</v>
       </c>
       <c r="B207" s="3"/>
-      <c r="C207" s="91" t="s">
+      <c r="C207" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D207" s="82" t="s">
@@ -11741,7 +11752,7 @@
     <row r="208" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A208" s="82"/>
       <c r="B208" s="4"/>
-      <c r="C208" s="92"/>
+      <c r="C208" s="89"/>
       <c r="D208" s="2" t="s">
         <v>81</v>
       </c>
@@ -12072,7 +12083,7 @@
         <v>1</v>
       </c>
       <c r="B220" s="3"/>
-      <c r="C220" s="91" t="s">
+      <c r="C220" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D220" s="82" t="s">
@@ -12096,7 +12107,7 @@
     <row r="221" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A221" s="82"/>
       <c r="B221" s="4"/>
-      <c r="C221" s="92"/>
+      <c r="C221" s="89"/>
       <c r="D221" s="2" t="s">
         <v>81</v>
       </c>
@@ -12427,7 +12438,7 @@
         <v>1</v>
       </c>
       <c r="B232" s="3"/>
-      <c r="C232" s="91" t="s">
+      <c r="C232" s="88" t="s">
         <v>105</v>
       </c>
       <c r="D232" s="82" t="s">
@@ -12451,7 +12462,7 @@
     <row r="233" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A233" s="82"/>
       <c r="B233" s="4"/>
-      <c r="C233" s="92"/>
+      <c r="C233" s="89"/>
       <c r="D233" s="2" t="s">
         <v>81</v>
       </c>
@@ -12782,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="B244" s="3"/>
-      <c r="C244" s="91" t="s">
+      <c r="C244" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D244" s="82" t="s">
@@ -12806,7 +12817,7 @@
     <row r="245" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A245" s="82"/>
       <c r="B245" s="4"/>
-      <c r="C245" s="92"/>
+      <c r="C245" s="89"/>
       <c r="D245" s="2" t="s">
         <v>81</v>
       </c>
@@ -13137,7 +13148,7 @@
         <v>1</v>
       </c>
       <c r="B256" s="3"/>
-      <c r="C256" s="91" t="s">
+      <c r="C256" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D256" s="82" t="s">
@@ -13161,7 +13172,7 @@
     <row r="257" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A257" s="82"/>
       <c r="B257" s="4"/>
-      <c r="C257" s="92"/>
+      <c r="C257" s="89"/>
       <c r="D257" s="2" t="s">
         <v>81</v>
       </c>
@@ -13492,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="B268" s="3"/>
-      <c r="C268" s="91" t="s">
+      <c r="C268" s="88" t="s">
         <v>101</v>
       </c>
       <c r="D268" s="82" t="s">
@@ -13516,7 +13527,7 @@
     <row r="269" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A269" s="82"/>
       <c r="B269" s="4"/>
-      <c r="C269" s="92"/>
+      <c r="C269" s="89"/>
       <c r="D269" s="2" t="s">
         <v>81</v>
       </c>
@@ -13847,7 +13858,7 @@
         <v>1</v>
       </c>
       <c r="B280" s="3"/>
-      <c r="C280" s="91" t="s">
+      <c r="C280" s="88" t="s">
         <v>106</v>
       </c>
       <c r="D280" s="82" t="s">
@@ -13871,7 +13882,7 @@
     <row r="281" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A281" s="82"/>
       <c r="B281" s="4"/>
-      <c r="C281" s="92"/>
+      <c r="C281" s="89"/>
       <c r="D281" s="2" t="s">
         <v>81</v>
       </c>
@@ -14201,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="B292" s="3"/>
-      <c r="C292" s="91" t="s">
+      <c r="C292" s="88" t="s">
         <v>106</v>
       </c>
       <c r="D292" s="82" t="s">
@@ -14225,7 +14236,7 @@
     <row r="293" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A293" s="82"/>
       <c r="B293" s="4"/>
-      <c r="C293" s="92"/>
+      <c r="C293" s="89"/>
       <c r="D293" s="2" t="s">
         <v>81</v>
       </c>
@@ -14555,7 +14566,7 @@
         <v>1</v>
       </c>
       <c r="B304" s="3"/>
-      <c r="C304" s="91" t="s">
+      <c r="C304" s="88" t="s">
         <v>106</v>
       </c>
       <c r="D304" s="82" t="s">
@@ -14579,7 +14590,7 @@
     <row r="305" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A305" s="82"/>
       <c r="B305" s="4"/>
-      <c r="C305" s="92"/>
+      <c r="C305" s="89"/>
       <c r="D305" s="2" t="s">
         <v>81</v>
       </c>
@@ -14909,7 +14920,7 @@
         <v>1</v>
       </c>
       <c r="B316" s="3"/>
-      <c r="C316" s="91" t="s">
+      <c r="C316" s="88" t="s">
         <v>110</v>
       </c>
       <c r="D316" s="82" t="s">
@@ -14933,7 +14944,7 @@
     <row r="317" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A317" s="82"/>
       <c r="B317" s="4"/>
-      <c r="C317" s="92"/>
+      <c r="C317" s="89"/>
       <c r="D317" s="2" t="s">
         <v>81</v>
       </c>
@@ -15263,7 +15274,7 @@
         <v>1</v>
       </c>
       <c r="B328" s="3"/>
-      <c r="C328" s="91" t="s">
+      <c r="C328" s="88" t="s">
         <v>110</v>
       </c>
       <c r="D328" s="82" t="s">
@@ -15287,7 +15298,7 @@
     <row r="329" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A329" s="82"/>
       <c r="B329" s="4"/>
-      <c r="C329" s="92"/>
+      <c r="C329" s="89"/>
       <c r="D329" s="2" t="s">
         <v>81</v>
       </c>
@@ -15617,7 +15628,7 @@
         <v>1</v>
       </c>
       <c r="B340" s="3"/>
-      <c r="C340" s="91" t="s">
+      <c r="C340" s="88" t="s">
         <v>110</v>
       </c>
       <c r="D340" s="82" t="s">
@@ -15641,7 +15652,7 @@
     <row r="341" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A341" s="82"/>
       <c r="B341" s="4"/>
-      <c r="C341" s="92"/>
+      <c r="C341" s="89"/>
       <c r="D341" s="2" t="s">
         <v>81</v>
       </c>
@@ -15971,7 +15982,7 @@
         <v>1</v>
       </c>
       <c r="B352" s="3"/>
-      <c r="C352" s="91" t="s">
+      <c r="C352" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D352" s="82" t="s">
@@ -15995,7 +16006,7 @@
     <row r="353" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A353" s="82"/>
       <c r="B353" s="4"/>
-      <c r="C353" s="92"/>
+      <c r="C353" s="89"/>
       <c r="D353" s="2" t="s">
         <v>81</v>
       </c>
@@ -16326,7 +16337,7 @@
         <v>1</v>
       </c>
       <c r="B364" s="3"/>
-      <c r="C364" s="91" t="s">
+      <c r="C364" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D364" s="82" t="s">
@@ -16350,7 +16361,7 @@
     <row r="365" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A365" s="82"/>
       <c r="B365" s="4"/>
-      <c r="C365" s="92"/>
+      <c r="C365" s="89"/>
       <c r="D365" s="2" t="s">
         <v>81</v>
       </c>
@@ -16681,7 +16692,7 @@
         <v>1</v>
       </c>
       <c r="B376" s="3"/>
-      <c r="C376" s="91" t="s">
+      <c r="C376" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D376" s="82" t="s">
@@ -16705,7 +16716,7 @@
     <row r="377" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A377" s="82"/>
       <c r="B377" s="4"/>
-      <c r="C377" s="92"/>
+      <c r="C377" s="89"/>
       <c r="D377" s="2" t="s">
         <v>81</v>
       </c>
@@ -17039,7 +17050,7 @@
         <v>1</v>
       </c>
       <c r="B388" s="3"/>
-      <c r="C388" s="91" t="s">
+      <c r="C388" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D388" s="82" t="s">
@@ -17063,7 +17074,7 @@
     <row r="389" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A389" s="82"/>
       <c r="B389" s="4"/>
-      <c r="C389" s="92"/>
+      <c r="C389" s="89"/>
       <c r="D389" s="2" t="s">
         <v>81</v>
       </c>
@@ -17395,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="B400" s="3"/>
-      <c r="C400" s="91" t="s">
+      <c r="C400" s="88" t="s">
         <v>114</v>
       </c>
       <c r="D400" s="82" t="s">
@@ -17419,7 +17430,7 @@
     <row r="401" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A401" s="82"/>
       <c r="B401" s="4"/>
-      <c r="C401" s="92"/>
+      <c r="C401" s="89"/>
       <c r="D401" s="2" t="s">
         <v>122</v>
       </c>
@@ -17770,20 +17781,20 @@
       <c r="A412" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B412" s="87" t="s">
+      <c r="B412" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C412" s="87" t="s">
+      <c r="C412" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D412" s="83" t="s">
+      <c r="D412" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E412" s="84"/>
-      <c r="F412" s="84"/>
-      <c r="G412" s="84"/>
-      <c r="H412" s="84"/>
-      <c r="I412" s="85"/>
+      <c r="E412" s="91"/>
+      <c r="F412" s="91"/>
+      <c r="G412" s="91"/>
+      <c r="H412" s="91"/>
+      <c r="I412" s="92"/>
       <c r="J412" s="82" t="s">
         <v>87</v>
       </c>
@@ -17796,8 +17807,8 @@
     </row>
     <row r="413" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A413" s="82"/>
-      <c r="B413" s="88"/>
-      <c r="C413" s="88"/>
+      <c r="B413" s="85"/>
+      <c r="C413" s="85"/>
       <c r="D413" s="2" t="s">
         <v>122</v>
       </c>
@@ -18161,20 +18172,20 @@
       <c r="A424" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B424" s="87" t="s">
+      <c r="B424" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C424" s="87" t="s">
+      <c r="C424" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D424" s="83" t="s">
+      <c r="D424" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E424" s="84"/>
-      <c r="F424" s="84"/>
-      <c r="G424" s="84"/>
-      <c r="H424" s="84"/>
-      <c r="I424" s="85"/>
+      <c r="E424" s="91"/>
+      <c r="F424" s="91"/>
+      <c r="G424" s="91"/>
+      <c r="H424" s="91"/>
+      <c r="I424" s="92"/>
       <c r="J424" s="82" t="s">
         <v>87</v>
       </c>
@@ -18187,8 +18198,8 @@
     </row>
     <row r="425" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A425" s="82"/>
-      <c r="B425" s="88"/>
-      <c r="C425" s="88"/>
+      <c r="B425" s="85"/>
+      <c r="C425" s="85"/>
       <c r="D425" s="2" t="s">
         <v>122</v>
       </c>
@@ -18552,20 +18563,20 @@
       <c r="A436" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B436" s="87" t="s">
+      <c r="B436" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C436" s="87" t="s">
+      <c r="C436" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D436" s="83" t="s">
+      <c r="D436" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E436" s="84"/>
-      <c r="F436" s="84"/>
-      <c r="G436" s="84"/>
-      <c r="H436" s="84"/>
-      <c r="I436" s="85"/>
+      <c r="E436" s="91"/>
+      <c r="F436" s="91"/>
+      <c r="G436" s="91"/>
+      <c r="H436" s="91"/>
+      <c r="I436" s="92"/>
       <c r="J436" s="82" t="s">
         <v>87</v>
       </c>
@@ -18578,8 +18589,8 @@
     </row>
     <row r="437" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A437" s="82"/>
-      <c r="B437" s="88"/>
-      <c r="C437" s="88"/>
+      <c r="B437" s="85"/>
+      <c r="C437" s="85"/>
       <c r="D437" s="2" t="s">
         <v>122</v>
       </c>
@@ -18943,20 +18954,20 @@
       <c r="A448" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B448" s="87" t="s">
+      <c r="B448" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C448" s="87" t="s">
+      <c r="C448" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D448" s="83" t="s">
+      <c r="D448" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E448" s="84"/>
-      <c r="F448" s="84"/>
-      <c r="G448" s="84"/>
-      <c r="H448" s="84"/>
-      <c r="I448" s="85"/>
+      <c r="E448" s="91"/>
+      <c r="F448" s="91"/>
+      <c r="G448" s="91"/>
+      <c r="H448" s="91"/>
+      <c r="I448" s="92"/>
       <c r="J448" s="82" t="s">
         <v>87</v>
       </c>
@@ -18969,8 +18980,8 @@
     </row>
     <row r="449" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A449" s="82"/>
-      <c r="B449" s="88"/>
-      <c r="C449" s="88"/>
+      <c r="B449" s="85"/>
+      <c r="C449" s="85"/>
       <c r="D449" s="2" t="s">
         <v>122</v>
       </c>
@@ -19334,20 +19345,20 @@
       <c r="A460" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B460" s="87" t="s">
+      <c r="B460" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C460" s="87" t="s">
+      <c r="C460" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D460" s="83" t="s">
+      <c r="D460" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E460" s="84"/>
-      <c r="F460" s="84"/>
-      <c r="G460" s="84"/>
-      <c r="H460" s="84"/>
-      <c r="I460" s="85"/>
+      <c r="E460" s="91"/>
+      <c r="F460" s="91"/>
+      <c r="G460" s="91"/>
+      <c r="H460" s="91"/>
+      <c r="I460" s="92"/>
       <c r="J460" s="82" t="s">
         <v>87</v>
       </c>
@@ -19360,8 +19371,8 @@
     </row>
     <row r="461" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A461" s="82"/>
-      <c r="B461" s="88"/>
-      <c r="C461" s="88"/>
+      <c r="B461" s="85"/>
+      <c r="C461" s="85"/>
       <c r="D461" s="2" t="s">
         <v>122</v>
       </c>
@@ -19725,20 +19736,20 @@
       <c r="A472" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B472" s="87" t="s">
+      <c r="B472" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C472" s="87" t="s">
+      <c r="C472" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D472" s="83" t="s">
+      <c r="D472" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E472" s="84"/>
-      <c r="F472" s="84"/>
-      <c r="G472" s="84"/>
-      <c r="H472" s="84"/>
-      <c r="I472" s="85"/>
+      <c r="E472" s="91"/>
+      <c r="F472" s="91"/>
+      <c r="G472" s="91"/>
+      <c r="H472" s="91"/>
+      <c r="I472" s="92"/>
       <c r="J472" s="82" t="s">
         <v>87</v>
       </c>
@@ -19751,8 +19762,8 @@
     </row>
     <row r="473" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A473" s="82"/>
-      <c r="B473" s="88"/>
-      <c r="C473" s="88"/>
+      <c r="B473" s="85"/>
+      <c r="C473" s="85"/>
       <c r="D473" s="2" t="s">
         <v>122</v>
       </c>
@@ -20116,20 +20127,20 @@
       <c r="A484" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B484" s="87" t="s">
+      <c r="B484" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C484" s="87" t="s">
+      <c r="C484" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D484" s="83" t="s">
+      <c r="D484" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E484" s="84"/>
-      <c r="F484" s="84"/>
-      <c r="G484" s="84"/>
-      <c r="H484" s="84"/>
-      <c r="I484" s="85"/>
+      <c r="E484" s="91"/>
+      <c r="F484" s="91"/>
+      <c r="G484" s="91"/>
+      <c r="H484" s="91"/>
+      <c r="I484" s="92"/>
       <c r="J484" s="82" t="s">
         <v>87</v>
       </c>
@@ -20142,8 +20153,8 @@
     </row>
     <row r="485" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A485" s="82"/>
-      <c r="B485" s="88"/>
-      <c r="C485" s="88"/>
+      <c r="B485" s="85"/>
+      <c r="C485" s="85"/>
       <c r="D485" s="2" t="s">
         <v>122</v>
       </c>
@@ -20507,20 +20518,20 @@
       <c r="A496" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B496" s="87" t="s">
+      <c r="B496" s="84" t="s">
         <v>123</v>
       </c>
-      <c r="C496" s="87" t="s">
+      <c r="C496" s="84" t="s">
         <v>124</v>
       </c>
-      <c r="D496" s="83" t="s">
+      <c r="D496" s="90" t="s">
         <v>86</v>
       </c>
-      <c r="E496" s="84"/>
-      <c r="F496" s="84"/>
-      <c r="G496" s="84"/>
-      <c r="H496" s="84"/>
-      <c r="I496" s="85"/>
+      <c r="E496" s="91"/>
+      <c r="F496" s="91"/>
+      <c r="G496" s="91"/>
+      <c r="H496" s="91"/>
+      <c r="I496" s="92"/>
       <c r="J496" s="82" t="s">
         <v>87</v>
       </c>
@@ -20533,8 +20544,8 @@
     </row>
     <row r="497" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A497" s="82"/>
-      <c r="B497" s="88"/>
-      <c r="C497" s="88"/>
+      <c r="B497" s="85"/>
+      <c r="C497" s="85"/>
       <c r="D497" s="2" t="s">
         <v>122</v>
       </c>
@@ -20903,10 +20914,10 @@
       <c r="A508" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="B508" s="87" t="s">
+      <c r="B508" s="84" t="s">
         <v>105</v>
       </c>
-      <c r="C508" s="87" t="s">
+      <c r="C508" s="84" t="s">
         <v>124</v>
       </c>
       <c r="D508" s="82" t="s">
@@ -20933,8 +20944,8 @@
     </row>
     <row r="509" spans="1:14" x14ac:dyDescent="0.15">
       <c r="A509" s="82"/>
-      <c r="B509" s="88"/>
-      <c r="C509" s="88"/>
+      <c r="B509" s="85"/>
+      <c r="C509" s="85"/>
       <c r="D509" s="2" t="s">
         <v>122</v>
       </c>
@@ -21349,41 +21360,41 @@
       </c>
     </row>
     <row r="520" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A520" s="86" t="s">
+      <c r="A520" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="B520" s="89" t="s">
+      <c r="B520" s="86" t="s">
         <v>105</v>
       </c>
-      <c r="C520" s="89" t="s">
+      <c r="C520" s="86" t="s">
         <v>124</v>
       </c>
-      <c r="D520" s="86" t="s">
+      <c r="D520" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="E520" s="86"/>
-      <c r="F520" s="86"/>
-      <c r="G520" s="86"/>
-      <c r="H520" s="86"/>
-      <c r="I520" s="86"/>
-      <c r="J520" s="86"/>
-      <c r="K520" s="86" t="s">
+      <c r="E520" s="83"/>
+      <c r="F520" s="83"/>
+      <c r="G520" s="83"/>
+      <c r="H520" s="83"/>
+      <c r="I520" s="83"/>
+      <c r="J520" s="83"/>
+      <c r="K520" s="83" t="s">
         <v>125</v>
       </c>
-      <c r="L520" s="86" t="s">
+      <c r="L520" s="83" t="s">
         <v>87</v>
       </c>
-      <c r="M520" s="86" t="s">
+      <c r="M520" s="83" t="s">
         <v>88</v>
       </c>
-      <c r="N520" s="86" t="s">
+      <c r="N520" s="83" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="521" spans="1:15" x14ac:dyDescent="0.15">
-      <c r="A521" s="86"/>
-      <c r="B521" s="90"/>
-      <c r="C521" s="90"/>
+      <c r="A521" s="83"/>
+      <c r="B521" s="87"/>
+      <c r="C521" s="87"/>
       <c r="D521" s="16" t="s">
         <v>122</v>
       </c>
@@ -21405,10 +21416,10 @@
       <c r="J521" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="K521" s="86"/>
-      <c r="L521" s="86"/>
-      <c r="M521" s="86"/>
-      <c r="N521" s="86"/>
+      <c r="K521" s="83"/>
+      <c r="L521" s="83"/>
+      <c r="M521" s="83"/>
+      <c r="N521" s="83"/>
     </row>
     <row r="522" spans="1:15" x14ac:dyDescent="0.15">
       <c r="A522" s="5" t="s">
@@ -21989,36 +22000,222 @@
     </row>
   </sheetData>
   <mergeCells count="270">
-    <mergeCell ref="N508:N509"/>
-    <mergeCell ref="N520:N521"/>
-    <mergeCell ref="L436:L437"/>
-    <mergeCell ref="L448:L449"/>
-    <mergeCell ref="L460:L461"/>
-    <mergeCell ref="L472:L473"/>
-    <mergeCell ref="L484:L485"/>
-    <mergeCell ref="L496:L497"/>
-    <mergeCell ref="L508:L509"/>
-    <mergeCell ref="L520:L521"/>
-    <mergeCell ref="M508:M509"/>
-    <mergeCell ref="M520:M521"/>
-    <mergeCell ref="L328:L329"/>
-    <mergeCell ref="L340:L341"/>
-    <mergeCell ref="L352:L353"/>
-    <mergeCell ref="L364:L365"/>
-    <mergeCell ref="L376:L377"/>
-    <mergeCell ref="L388:L389"/>
-    <mergeCell ref="L400:L401"/>
-    <mergeCell ref="L412:L413"/>
-    <mergeCell ref="L424:L425"/>
-    <mergeCell ref="L220:L221"/>
-    <mergeCell ref="L232:L233"/>
-    <mergeCell ref="L244:L245"/>
-    <mergeCell ref="L256:L257"/>
-    <mergeCell ref="L268:L269"/>
-    <mergeCell ref="L280:L281"/>
-    <mergeCell ref="L292:L293"/>
-    <mergeCell ref="L304:L305"/>
-    <mergeCell ref="L316:L317"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="D53:I53"/>
+    <mergeCell ref="D65:I65"/>
+    <mergeCell ref="D78:I78"/>
+    <mergeCell ref="D91:I91"/>
+    <mergeCell ref="D104:I104"/>
+    <mergeCell ref="D117:I117"/>
+    <mergeCell ref="D130:I130"/>
+    <mergeCell ref="D143:I143"/>
+    <mergeCell ref="D156:I156"/>
+    <mergeCell ref="D169:I169"/>
+    <mergeCell ref="D181:I181"/>
+    <mergeCell ref="D194:I194"/>
+    <mergeCell ref="D207:I207"/>
+    <mergeCell ref="D220:I220"/>
+    <mergeCell ref="D232:I232"/>
+    <mergeCell ref="D244:I244"/>
+    <mergeCell ref="D256:I256"/>
+    <mergeCell ref="D268:I268"/>
+    <mergeCell ref="D280:I280"/>
+    <mergeCell ref="D292:I292"/>
+    <mergeCell ref="D304:I304"/>
+    <mergeCell ref="D316:I316"/>
+    <mergeCell ref="D328:I328"/>
+    <mergeCell ref="D340:I340"/>
+    <mergeCell ref="D352:I352"/>
+    <mergeCell ref="D364:I364"/>
+    <mergeCell ref="D376:I376"/>
+    <mergeCell ref="D388:I388"/>
+    <mergeCell ref="D400:I400"/>
+    <mergeCell ref="D412:I412"/>
+    <mergeCell ref="D424:I424"/>
+    <mergeCell ref="D436:I436"/>
+    <mergeCell ref="D448:I448"/>
+    <mergeCell ref="D460:I460"/>
+    <mergeCell ref="D472:I472"/>
+    <mergeCell ref="D484:I484"/>
+    <mergeCell ref="D496:I496"/>
+    <mergeCell ref="D508:J508"/>
+    <mergeCell ref="D520:J520"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A78:A79"/>
+    <mergeCell ref="A91:A92"/>
+    <mergeCell ref="A104:A105"/>
+    <mergeCell ref="A117:A118"/>
+    <mergeCell ref="A130:A131"/>
+    <mergeCell ref="A143:A144"/>
+    <mergeCell ref="A156:A157"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A181:A182"/>
+    <mergeCell ref="A194:A195"/>
+    <mergeCell ref="A207:A208"/>
+    <mergeCell ref="A220:A221"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="A244:A245"/>
+    <mergeCell ref="A256:A257"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="A280:A281"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="A304:A305"/>
+    <mergeCell ref="A316:A317"/>
+    <mergeCell ref="A328:A329"/>
+    <mergeCell ref="A340:A341"/>
+    <mergeCell ref="A352:A353"/>
+    <mergeCell ref="A364:A365"/>
+    <mergeCell ref="A376:A377"/>
+    <mergeCell ref="A388:A389"/>
+    <mergeCell ref="A400:A401"/>
+    <mergeCell ref="A412:A413"/>
+    <mergeCell ref="A424:A425"/>
+    <mergeCell ref="A436:A437"/>
+    <mergeCell ref="A448:A449"/>
+    <mergeCell ref="A460:A461"/>
+    <mergeCell ref="A472:A473"/>
+    <mergeCell ref="A484:A485"/>
+    <mergeCell ref="A496:A497"/>
+    <mergeCell ref="A508:A509"/>
+    <mergeCell ref="A520:A521"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="B484:B485"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C53:C54"/>
+    <mergeCell ref="C65:C66"/>
+    <mergeCell ref="C78:C79"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="C104:C105"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="C130:C131"/>
+    <mergeCell ref="C143:C144"/>
+    <mergeCell ref="C156:C157"/>
+    <mergeCell ref="C169:C170"/>
+    <mergeCell ref="C181:C182"/>
+    <mergeCell ref="C194:C195"/>
+    <mergeCell ref="C207:C208"/>
+    <mergeCell ref="C220:C221"/>
+    <mergeCell ref="C232:C233"/>
+    <mergeCell ref="C244:C245"/>
+    <mergeCell ref="C256:C257"/>
+    <mergeCell ref="C268:C269"/>
+    <mergeCell ref="C280:C281"/>
+    <mergeCell ref="C292:C293"/>
+    <mergeCell ref="C304:C305"/>
+    <mergeCell ref="C316:C317"/>
+    <mergeCell ref="C328:C329"/>
+    <mergeCell ref="C340:C341"/>
+    <mergeCell ref="C352:C353"/>
+    <mergeCell ref="C364:C365"/>
+    <mergeCell ref="C376:C377"/>
+    <mergeCell ref="C388:C389"/>
+    <mergeCell ref="C400:C401"/>
+    <mergeCell ref="C412:C413"/>
+    <mergeCell ref="C424:C425"/>
+    <mergeCell ref="C436:C437"/>
+    <mergeCell ref="C448:C449"/>
+    <mergeCell ref="C460:C461"/>
+    <mergeCell ref="C472:C473"/>
+    <mergeCell ref="C484:C485"/>
+    <mergeCell ref="C496:C497"/>
+    <mergeCell ref="C508:C509"/>
+    <mergeCell ref="C520:C521"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="J29:J30"/>
+    <mergeCell ref="J41:J42"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="J78:J79"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="J104:J105"/>
+    <mergeCell ref="J117:J118"/>
+    <mergeCell ref="J130:J131"/>
+    <mergeCell ref="J143:J144"/>
+    <mergeCell ref="J156:J157"/>
+    <mergeCell ref="J169:J170"/>
+    <mergeCell ref="J181:J182"/>
+    <mergeCell ref="J194:J195"/>
+    <mergeCell ref="J207:J208"/>
+    <mergeCell ref="J220:J221"/>
+    <mergeCell ref="J232:J233"/>
+    <mergeCell ref="J244:J245"/>
+    <mergeCell ref="J256:J257"/>
+    <mergeCell ref="J268:J269"/>
+    <mergeCell ref="J280:J281"/>
+    <mergeCell ref="J292:J293"/>
+    <mergeCell ref="J304:J305"/>
+    <mergeCell ref="J316:J317"/>
+    <mergeCell ref="J328:J329"/>
+    <mergeCell ref="J340:J341"/>
+    <mergeCell ref="J352:J353"/>
+    <mergeCell ref="J364:J365"/>
+    <mergeCell ref="J376:J377"/>
+    <mergeCell ref="J388:J389"/>
+    <mergeCell ref="J400:J401"/>
+    <mergeCell ref="J412:J413"/>
+    <mergeCell ref="J424:J425"/>
+    <mergeCell ref="J436:J437"/>
+    <mergeCell ref="J448:J449"/>
+    <mergeCell ref="J460:J461"/>
+    <mergeCell ref="J472:J473"/>
+    <mergeCell ref="J484:J485"/>
+    <mergeCell ref="J496:J497"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="K29:K30"/>
+    <mergeCell ref="K41:K42"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="K65:K66"/>
+    <mergeCell ref="K78:K79"/>
+    <mergeCell ref="K91:K92"/>
+    <mergeCell ref="K104:K105"/>
+    <mergeCell ref="K117:K118"/>
+    <mergeCell ref="K130:K131"/>
+    <mergeCell ref="K143:K144"/>
+    <mergeCell ref="K156:K157"/>
+    <mergeCell ref="K169:K170"/>
+    <mergeCell ref="K181:K182"/>
+    <mergeCell ref="K194:K195"/>
+    <mergeCell ref="K207:K208"/>
+    <mergeCell ref="K220:K221"/>
+    <mergeCell ref="K232:K233"/>
+    <mergeCell ref="K244:K245"/>
+    <mergeCell ref="K256:K257"/>
+    <mergeCell ref="K268:K269"/>
+    <mergeCell ref="K280:K281"/>
+    <mergeCell ref="K292:K293"/>
+    <mergeCell ref="K304:K305"/>
+    <mergeCell ref="K316:K317"/>
+    <mergeCell ref="K328:K329"/>
+    <mergeCell ref="K340:K341"/>
+    <mergeCell ref="K352:K353"/>
+    <mergeCell ref="K364:K365"/>
+    <mergeCell ref="K376:K377"/>
+    <mergeCell ref="K388:K389"/>
+    <mergeCell ref="K400:K401"/>
+    <mergeCell ref="K412:K413"/>
+    <mergeCell ref="K424:K425"/>
+    <mergeCell ref="K436:K437"/>
     <mergeCell ref="K448:K449"/>
     <mergeCell ref="K460:K461"/>
     <mergeCell ref="K472:K473"/>
@@ -22043,222 +22240,36 @@
     <mergeCell ref="L181:L182"/>
     <mergeCell ref="L194:L195"/>
     <mergeCell ref="L207:L208"/>
-    <mergeCell ref="K340:K341"/>
-    <mergeCell ref="K352:K353"/>
-    <mergeCell ref="K364:K365"/>
-    <mergeCell ref="K376:K377"/>
-    <mergeCell ref="K388:K389"/>
-    <mergeCell ref="K400:K401"/>
-    <mergeCell ref="K412:K413"/>
-    <mergeCell ref="K424:K425"/>
-    <mergeCell ref="K436:K437"/>
-    <mergeCell ref="K232:K233"/>
-    <mergeCell ref="K244:K245"/>
-    <mergeCell ref="K256:K257"/>
-    <mergeCell ref="K268:K269"/>
-    <mergeCell ref="K280:K281"/>
-    <mergeCell ref="K292:K293"/>
-    <mergeCell ref="K304:K305"/>
-    <mergeCell ref="K316:K317"/>
-    <mergeCell ref="K328:K329"/>
-    <mergeCell ref="J436:J437"/>
-    <mergeCell ref="J448:J449"/>
-    <mergeCell ref="J460:J461"/>
-    <mergeCell ref="J472:J473"/>
-    <mergeCell ref="J484:J485"/>
-    <mergeCell ref="J496:J497"/>
-    <mergeCell ref="K1:K2"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="K29:K30"/>
-    <mergeCell ref="K41:K42"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="K65:K66"/>
-    <mergeCell ref="K78:K79"/>
-    <mergeCell ref="K91:K92"/>
-    <mergeCell ref="K104:K105"/>
-    <mergeCell ref="K117:K118"/>
-    <mergeCell ref="K130:K131"/>
-    <mergeCell ref="K143:K144"/>
-    <mergeCell ref="K156:K157"/>
-    <mergeCell ref="K169:K170"/>
-    <mergeCell ref="K181:K182"/>
-    <mergeCell ref="K194:K195"/>
-    <mergeCell ref="K207:K208"/>
-    <mergeCell ref="K220:K221"/>
-    <mergeCell ref="J328:J329"/>
-    <mergeCell ref="J340:J341"/>
-    <mergeCell ref="J352:J353"/>
-    <mergeCell ref="J364:J365"/>
-    <mergeCell ref="J376:J377"/>
-    <mergeCell ref="J388:J389"/>
-    <mergeCell ref="J400:J401"/>
-    <mergeCell ref="J412:J413"/>
-    <mergeCell ref="J424:J425"/>
-    <mergeCell ref="J220:J221"/>
-    <mergeCell ref="J232:J233"/>
-    <mergeCell ref="J244:J245"/>
-    <mergeCell ref="J256:J257"/>
-    <mergeCell ref="J268:J269"/>
-    <mergeCell ref="J280:J281"/>
-    <mergeCell ref="J292:J293"/>
-    <mergeCell ref="J304:J305"/>
-    <mergeCell ref="J316:J317"/>
-    <mergeCell ref="C448:C449"/>
-    <mergeCell ref="C460:C461"/>
-    <mergeCell ref="C472:C473"/>
-    <mergeCell ref="C484:C485"/>
-    <mergeCell ref="C496:C497"/>
-    <mergeCell ref="C508:C509"/>
-    <mergeCell ref="C520:C521"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="J29:J30"/>
-    <mergeCell ref="J41:J42"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="J78:J79"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="J104:J105"/>
-    <mergeCell ref="J117:J118"/>
-    <mergeCell ref="J130:J131"/>
-    <mergeCell ref="J143:J144"/>
-    <mergeCell ref="J156:J157"/>
-    <mergeCell ref="J169:J170"/>
-    <mergeCell ref="J181:J182"/>
-    <mergeCell ref="J194:J195"/>
-    <mergeCell ref="J207:J208"/>
-    <mergeCell ref="C340:C341"/>
-    <mergeCell ref="C352:C353"/>
-    <mergeCell ref="C364:C365"/>
-    <mergeCell ref="C376:C377"/>
-    <mergeCell ref="C388:C389"/>
-    <mergeCell ref="C400:C401"/>
-    <mergeCell ref="C412:C413"/>
-    <mergeCell ref="C424:C425"/>
-    <mergeCell ref="C436:C437"/>
-    <mergeCell ref="C232:C233"/>
-    <mergeCell ref="C244:C245"/>
-    <mergeCell ref="C256:C257"/>
-    <mergeCell ref="C268:C269"/>
-    <mergeCell ref="C280:C281"/>
-    <mergeCell ref="C292:C293"/>
-    <mergeCell ref="C304:C305"/>
-    <mergeCell ref="C316:C317"/>
-    <mergeCell ref="C328:C329"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="C130:C131"/>
-    <mergeCell ref="C143:C144"/>
-    <mergeCell ref="C156:C157"/>
-    <mergeCell ref="C169:C170"/>
-    <mergeCell ref="C181:C182"/>
-    <mergeCell ref="C194:C195"/>
-    <mergeCell ref="C207:C208"/>
-    <mergeCell ref="C220:C221"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="C29:C30"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C53:C54"/>
-    <mergeCell ref="C65:C66"/>
-    <mergeCell ref="C78:C79"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="C104:C105"/>
-    <mergeCell ref="A436:A437"/>
-    <mergeCell ref="A448:A449"/>
-    <mergeCell ref="A460:A461"/>
-    <mergeCell ref="A472:A473"/>
-    <mergeCell ref="A484:A485"/>
-    <mergeCell ref="A496:A497"/>
-    <mergeCell ref="A508:A509"/>
-    <mergeCell ref="A520:A521"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="B484:B485"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="A328:A329"/>
-    <mergeCell ref="A340:A341"/>
-    <mergeCell ref="A352:A353"/>
-    <mergeCell ref="A364:A365"/>
-    <mergeCell ref="A376:A377"/>
-    <mergeCell ref="A388:A389"/>
-    <mergeCell ref="A400:A401"/>
-    <mergeCell ref="A412:A413"/>
-    <mergeCell ref="A424:A425"/>
-    <mergeCell ref="A220:A221"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="A244:A245"/>
-    <mergeCell ref="A256:A257"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="A280:A281"/>
-    <mergeCell ref="A292:A293"/>
-    <mergeCell ref="A304:A305"/>
-    <mergeCell ref="A316:A317"/>
-    <mergeCell ref="D448:I448"/>
-    <mergeCell ref="D460:I460"/>
-    <mergeCell ref="D472:I472"/>
-    <mergeCell ref="D484:I484"/>
-    <mergeCell ref="D496:I496"/>
-    <mergeCell ref="D508:J508"/>
-    <mergeCell ref="D520:J520"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="A41:A42"/>
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A78:A79"/>
-    <mergeCell ref="A91:A92"/>
-    <mergeCell ref="A104:A105"/>
-    <mergeCell ref="A117:A118"/>
-    <mergeCell ref="A130:A131"/>
-    <mergeCell ref="A143:A144"/>
-    <mergeCell ref="A156:A157"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A181:A182"/>
-    <mergeCell ref="A194:A195"/>
-    <mergeCell ref="A207:A208"/>
-    <mergeCell ref="D340:I340"/>
-    <mergeCell ref="D352:I352"/>
-    <mergeCell ref="D364:I364"/>
-    <mergeCell ref="D376:I376"/>
-    <mergeCell ref="D388:I388"/>
-    <mergeCell ref="D400:I400"/>
-    <mergeCell ref="D412:I412"/>
-    <mergeCell ref="D424:I424"/>
-    <mergeCell ref="D436:I436"/>
-    <mergeCell ref="D232:I232"/>
-    <mergeCell ref="D244:I244"/>
-    <mergeCell ref="D256:I256"/>
-    <mergeCell ref="D268:I268"/>
-    <mergeCell ref="D280:I280"/>
-    <mergeCell ref="D292:I292"/>
-    <mergeCell ref="D304:I304"/>
-    <mergeCell ref="D316:I316"/>
-    <mergeCell ref="D328:I328"/>
-    <mergeCell ref="D117:I117"/>
-    <mergeCell ref="D130:I130"/>
-    <mergeCell ref="D143:I143"/>
-    <mergeCell ref="D156:I156"/>
-    <mergeCell ref="D169:I169"/>
-    <mergeCell ref="D181:I181"/>
-    <mergeCell ref="D194:I194"/>
-    <mergeCell ref="D207:I207"/>
-    <mergeCell ref="D220:I220"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D15:I15"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="D53:I53"/>
-    <mergeCell ref="D65:I65"/>
-    <mergeCell ref="D78:I78"/>
-    <mergeCell ref="D91:I91"/>
-    <mergeCell ref="D104:I104"/>
+    <mergeCell ref="L220:L221"/>
+    <mergeCell ref="L232:L233"/>
+    <mergeCell ref="L244:L245"/>
+    <mergeCell ref="L256:L257"/>
+    <mergeCell ref="L268:L269"/>
+    <mergeCell ref="L280:L281"/>
+    <mergeCell ref="L292:L293"/>
+    <mergeCell ref="L304:L305"/>
+    <mergeCell ref="L316:L317"/>
+    <mergeCell ref="L328:L329"/>
+    <mergeCell ref="L340:L341"/>
+    <mergeCell ref="L352:L353"/>
+    <mergeCell ref="L364:L365"/>
+    <mergeCell ref="L376:L377"/>
+    <mergeCell ref="L388:L389"/>
+    <mergeCell ref="L400:L401"/>
+    <mergeCell ref="L412:L413"/>
+    <mergeCell ref="L424:L425"/>
+    <mergeCell ref="N508:N509"/>
+    <mergeCell ref="N520:N521"/>
+    <mergeCell ref="L436:L437"/>
+    <mergeCell ref="L448:L449"/>
+    <mergeCell ref="L460:L461"/>
+    <mergeCell ref="L472:L473"/>
+    <mergeCell ref="L484:L485"/>
+    <mergeCell ref="L496:L497"/>
+    <mergeCell ref="L508:L509"/>
+    <mergeCell ref="L520:L521"/>
+    <mergeCell ref="M508:M509"/>
+    <mergeCell ref="M520:M521"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <conditionalFormatting sqref="L3:L9">
